--- a/StructureDefinition-inera-ehds-medication-statement.xlsx
+++ b/StructureDefinition-inera-ehds-medication-statement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:52:35+00:00</t>
+    <t>2026-09-30T09:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -788,8 +788,8 @@
     <t>MedicationStatement.medication[x]</t>
   </si>
   <si>
-    <t>CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
-Reference(http://hl7.org/fhir/uv/ips/StructureDefinition/Medication-uv-ips)</t>
+    <t>CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips|2.0.1}
+Reference(http://hl7.org/fhir/uv/ips/StructureDefinition/Medication-uv-ips|2.0.1)</t>
   </si>
   <si>
     <t>Läkemedel (medicationMedicalRecordBody.medicationPrescription.drug – XOR: unstructured/merchandise/drugArticle/drug/generics, se MED-003)</t>
@@ -804,7 +804,7 @@
     <t>SNOMED CT medications (Medicinal product) or a code for absent/unknown medication</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/medication-uv-ips</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/medication-uv-ips|2.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1408,7 +1408,7 @@
     <t>SNOMED Route Terms</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
   </si>
   <si>
     <t>Dosage.route</t>

--- a/StructureDefinition-inera-ehds-medication-statement.xlsx
+++ b/StructureDefinition-inera-ehds-medication-statement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:02:48+00:00</t>
+    <t>2026-09-30T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-medication-statement.xlsx
+++ b/StructureDefinition-inera-ehds-medication-statement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:52:57+00:00</t>
+    <t>2026-10-01T18:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-medication-statement.xlsx
+++ b/StructureDefinition-inera-ehds-medication-statement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T18:35:17+00:00</t>
+    <t>2026-10-02T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -433,7 +433,7 @@
 </t>
   </si>
   <si>
-    <t>Källsystem HSA-id (medicationMedicalRecordHeader.sourceSystemHSAId)</t>
+    <t>Källsystem HSA-id (medicationMedicalRecordHeader.sourceSystemHSAId) – https://tjanstekatalogen.inera.se/Endpoint/{hsaId} (GENERAL-005)</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -788,8 +788,8 @@
     <t>MedicationStatement.medication[x]</t>
   </si>
   <si>
-    <t>CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips|2.0.1}
-Reference(http://hl7.org/fhir/uv/ips/StructureDefinition/Medication-uv-ips|2.0.1)</t>
+    <t>CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
+Reference(http://hl7.org/fhir/uv/ips/StructureDefinition/Medication-uv-ips)</t>
   </si>
   <si>
     <t>Läkemedel (medicationMedicalRecordBody.medicationPrescription.drug – XOR: unstructured/merchandise/drugArticle/drug/generics, se MED-003)</t>
@@ -804,7 +804,7 @@
     <t>SNOMED CT medications (Medicinal product) or a code for absent/unknown medication</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/medication-uv-ips|2.0.1</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/medication-uv-ips</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1408,7 +1408,7 @@
     <t>SNOMED Route Terms</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/route-codes</t>
   </si>
   <si>
     <t>Dosage.route</t>
